--- a/output/projects/Mala/excel/ArbetsExcel_Mala_byggd.xlsx
+++ b/output/projects/Mala/excel/ArbetsExcel_Mala_byggd.xlsx
@@ -10,10 +10,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Taxa_från_edp" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Körningsinfo" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Taxa_Förslag" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regelspårning" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDP_Standard_Standard Avfall" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDP_Standard_Standard Slam" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDP_Standard_Standard ÅVS" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDP_Avviker_Standard" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regelspårning" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDP_Standard_Standard Avfall" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDP_Standard_Standard Slam" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDP_Standard_Standard ÅVS" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -600,7 +601,28 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RegelsparningTable" displayName="RegelsparningTable" ref="A6:J7" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EdpAvvikerStandardTable" displayName="EdpAvvikerStandardTable" ref="A6:L7" headerRowCount="1">
+  <autoFilter ref="A6:L7"/>
+  <tableColumns count="12">
+    <tableColumn id="1" name="Kommun"/>
+    <tableColumn id="2" name="EDP taxekod"/>
+    <tableColumn id="3" name="EDP benämning"/>
+    <tableColumn id="4" name="EDP faktor"/>
+    <tableColumn id="5" name="EDP taxedel"/>
+    <tableColumn id="6" name="Standard taxekod"/>
+    <tableColumn id="7" name="Standard benämning"/>
+    <tableColumn id="8" name="Standard faktor"/>
+    <tableColumn id="9" name="Standard taxedel"/>
+    <tableColumn id="10" name="Avvikelse"/>
+    <tableColumn id="11" name="Rekommendation"/>
+    <tableColumn id="12" name="Status"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="RegelsparningTable" displayName="RegelsparningTable" ref="A6:J7" headerRowCount="1">
   <autoFilter ref="A6:J7"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Kommun"/>
@@ -23221,7 +23243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -23289,36 +23311,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Standardtaxor</t>
+          <t>EDP-regel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Inkluderade som referensflikar om standardtaxefilen finns</t>
+          <t>Taxor i Taxa_från_edp är fasta och ändras inte automatiskt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Taxa_Förslag</t>
+          <t>Standardtaxor</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ingår i alla outputfiler för föreslagna saknade taxekoder</t>
+          <t>Inkluderade som referensflikar om standardtaxefilen finns</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Taxa_Förslag</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ingår för föreslagna saknade taxekoder</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EDP_Avviker_Standard</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ingår för avvikelser mot standardtaxor</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Regelspårning</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Ingår i alla outputfiler för spårbarhet av beslut/regler</t>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ingår för spårbarhet av beslut/regler</t>
         </is>
       </c>
     </row>
@@ -23492,6 +23538,168 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+    <col width="54" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>EDP Export avviker från standardtaxa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Syfte</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Visar avvikelser mot standardtaxor. Befintlig Taxa_från_edp är fast och ändras aldrig automatiskt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Kommun</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Malå</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Källa</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>EDP-export: data\edp_exports\Mala.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Kommun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>EDP taxekod</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>EDP benämning</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>EDP faktor</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>EDP taxedel</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Standard taxekod</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Standard benämning</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Standard faktor</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Standard taxedel</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Avvikelse</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Rekommendation</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Malå</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>Granska manuellt. Ändra inte befintlig EDP automatiskt.</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -23501,7 +23709,7 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="50" customWidth="1" min="10" max="10"/>
@@ -23623,7 +23831,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Taxakod får endast sättas från säker EDP-match eller markerat förslag.</t>
+          <t>Befintlig Taxa_från_edp är fast. Standardtaxor får endast ge förslag/avvikelse.</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -23650,7 +23858,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37090,7 +37298,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40763,7 +40971,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/output/projects/Mala/excel/ArbetsExcel_Mala_byggd.xlsx
+++ b/output/projects/Mala/excel/ArbetsExcel_Mala_byggd.xlsx
@@ -1079,8 +1079,6 @@
           <t>140L kärl - viktavgift matavfall</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>1.84</t>
@@ -1096,7 +1094,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>-</t>
@@ -1154,8 +1151,6 @@
           <t>Överviktsavgift för vikt över 60 kg, matavfall</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>3.68</t>
@@ -1171,7 +1166,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>-</t>
@@ -1229,8 +1223,6 @@
           <t>140-370L kärl - viktavgift restavfall</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>3.68</t>
@@ -1246,7 +1238,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>-</t>
@@ -1304,8 +1295,6 @@
           <t>Överviktsavgift för vikt över 60 kg, restavfall</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>7.36</t>
@@ -1321,7 +1310,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>-</t>
@@ -1379,8 +1367,6 @@
           <t>Asbest (inplastat, tätslutande)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>1400.0</t>
@@ -1396,7 +1382,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>-</t>
@@ -1454,8 +1439,6 @@
           <t>ÅVC-Avgift nivå 1</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>2600.0</t>
@@ -1471,7 +1454,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>-</t>
@@ -1482,7 +1464,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1525,8 +1506,6 @@
           <t>ÅVC-Avgift nivå 2</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>4300.0</t>
@@ -1542,7 +1521,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>-</t>
@@ -1553,7 +1531,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1596,8 +1573,6 @@
           <t>Fettavskiljare 0-2 m³. Budning</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1613,7 +1588,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>-</t>
@@ -1671,16 +1645,11 @@
           <t>Avslut av tjänst</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>-</t>
@@ -1738,8 +1707,6 @@
           <t>Oljeavskiljare. Budning</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1755,7 +1722,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>-</t>
@@ -1793,7 +1759,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>1</t>
@@ -1809,8 +1774,6 @@
           <t>Avstängning/strypning av vattentillförsel</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>1280.0</t>
@@ -1826,7 +1789,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>-</t>
@@ -1884,8 +1846,6 @@
           <t>Tömning BDT-vatten, 0-3 m³</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>1250.4</t>
@@ -1901,7 +1861,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>-</t>
@@ -1959,8 +1918,6 @@
           <t>BDT 0-3 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1976,7 +1933,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>-</t>
@@ -2034,8 +1990,6 @@
           <t>BDT 0-3 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2051,7 +2005,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>-</t>
@@ -2109,8 +2062,6 @@
           <t>BDT över 3 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2126,7 +2077,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>-</t>
@@ -2184,8 +2134,6 @@
           <t>BDT över 3 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2201,7 +2149,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>-</t>
@@ -2259,8 +2206,6 @@
           <t>Avgift för betalsäck</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>80.0</t>
@@ -2276,7 +2221,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>-</t>
@@ -2334,8 +2278,6 @@
           <t>Tömning slam, brunn 0-3 m³</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>1252.0</t>
@@ -2351,7 +2293,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>-</t>
@@ -2409,8 +2350,6 @@
           <t>Brunn 0-3 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2426,7 +2365,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>-</t>
@@ -2484,8 +2422,6 @@
           <t>Brunn 0-3 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2501,7 +2437,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>-</t>
@@ -2559,8 +2494,6 @@
           <t>Tömning slam, brunn 3,1-6 m³</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>1756.0</t>
@@ -2576,7 +2509,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>-</t>
@@ -2634,8 +2566,6 @@
           <t>Brunn 3,1-6 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2651,7 +2581,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>-</t>
@@ -2709,8 +2638,6 @@
           <t>Brunn 3,1-6 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2726,7 +2653,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>-</t>
@@ -2784,8 +2710,6 @@
           <t>Tömning slam, brunn över 6,1 m³</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>3254.4</t>
@@ -2801,7 +2725,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>-</t>
@@ -2859,8 +2782,6 @@
           <t>Brunn 6,1-9 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2876,7 +2797,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>-</t>
@@ -2934,8 +2854,6 @@
           <t>Brunn 6,1-9 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2951,7 +2869,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>-</t>
@@ -3009,8 +2926,6 @@
           <t>Brunn över 9 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3026,7 +2941,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>-</t>
@@ -3084,8 +2998,6 @@
           <t>Brunn över 9 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3101,7 +3013,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>-</t>
@@ -3159,8 +3070,6 @@
           <t>Brännbart avfall 80x20x20cm</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>2120.0</t>
@@ -3176,7 +3085,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>-</t>
@@ -3234,8 +3142,6 @@
           <t>Brännbart avfall 80x20x20cm</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>1800.0</t>
@@ -3251,7 +3157,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
           <t>-</t>
@@ -3309,8 +3214,6 @@
           <t>Brännbart avfall överstort</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>2496.0</t>
@@ -3326,7 +3229,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
           <t>-</t>
@@ -3384,8 +3286,6 @@
           <t>Brännbart avfall överstort</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>2600.0</t>
@@ -3401,7 +3301,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
           <t>-</t>
@@ -3459,8 +3358,6 @@
           <t>Budning av kommunalt avfall, framkörningsavgift</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>320.0</t>
@@ -3476,7 +3373,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
           <t>-</t>
@@ -3534,8 +3430,6 @@
           <t>Byggvatten, Rörlig avgift, förbrukning per m³</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>13.0</t>
@@ -3551,7 +3445,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
           <t>-</t>
@@ -3562,7 +3455,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3605,8 +3497,6 @@
           <t>Byggvatten, Rörlig avgift, uppsk. förbrukning per m³</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>13.0</t>
@@ -3622,7 +3512,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
           <t>-</t>
@@ -3633,7 +3522,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3676,8 +3564,6 @@
           <t>Bygg och rivningsavfall sorterat 80x20x20cm</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>2000.0</t>
@@ -3693,7 +3579,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>-</t>
@@ -3751,8 +3636,6 @@
           <t>Tjänsttaxa container för matavfall</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3768,7 +3651,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
           <t>-</t>
@@ -3826,8 +3708,6 @@
           <t>Tjänsttaxa container för restavfall</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3843,7 +3723,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
           <t>-</t>
@@ -3901,8 +3780,6 @@
           <t>Avgift för ej rengjort kärl vid kärlbyte</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>200.0</t>
@@ -3918,7 +3795,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
           <t>-</t>
@@ -3976,8 +3852,6 @@
           <t>Evenemang framkörningsavgift</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>400.0</t>
@@ -3993,7 +3867,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
           <t>-</t>
@@ -4051,8 +3924,6 @@
           <t>Tillfällig hyra evenemangskärl 140 L, matavfall</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>144.0</t>
@@ -4068,7 +3939,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>-</t>
@@ -4126,8 +3996,6 @@
           <t>Tillfällig hyra evenemangskärl 190 L, restavfall</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>160.0</t>
@@ -4143,7 +4011,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
           <t>-</t>
@@ -4201,8 +4068,6 @@
           <t>Tillfällig hyra evenemangskärl 370 L, restavfall</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>160.0</t>
@@ -4218,7 +4083,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
           <t>-</t>
@@ -4276,8 +4140,6 @@
           <t>Tillfällig hyra evenemangskärl 660 L, restavfall</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>344.0</t>
@@ -4293,7 +4155,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
           <t>-</t>
@@ -4351,8 +4212,6 @@
           <t>Tjänsttaxa för tillfälliga evenemangskärl</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4368,7 +4227,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
           <t>-</t>
@@ -4426,8 +4284,6 @@
           <t>Fast avgift vatten/spillvatten</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>1622.0</t>
@@ -4443,7 +4299,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>-</t>
@@ -4454,7 +4309,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4497,8 +4351,6 @@
           <t>Tjänsttaxa för farligt avfall</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4514,7 +4366,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>-</t>
@@ -4572,8 +4423,6 @@
           <t>Miljöfarligt avfall</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4589,7 +4438,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>-</t>
@@ -4647,8 +4495,6 @@
           <t>Budning av farligt avfall, pris per tillfälle</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>1120.0</t>
@@ -4664,7 +4510,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
           <t>-</t>
@@ -4722,8 +4567,6 @@
           <t>Felsorteringsavgift</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>400.0</t>
@@ -4739,7 +4582,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
           <t>-</t>
@@ -4797,8 +4639,6 @@
           <t>Statistik vikt fett</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4814,7 +4654,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
           <t>-</t>
@@ -4872,8 +4711,6 @@
           <t>Fosforfälla. Budning</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4889,7 +4726,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
           <t>-</t>
@@ -4947,8 +4783,6 @@
           <t>Fönster inklusive glas</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>200.0</t>
@@ -4964,7 +4798,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
           <t>-</t>
@@ -5002,7 +4835,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>1</t>
@@ -5018,8 +4850,6 @@
           <t>Förgävesbesök vid avtalad tid eller avisering</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>880.0</t>
@@ -5035,7 +4865,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
           <t>-</t>
@@ -5093,8 +4922,6 @@
           <t>Extra telefonnyckel till ÅVS</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>80.0</t>
@@ -5110,7 +4937,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
           <t>-</t>
@@ -5121,7 +4947,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5164,8 +4989,6 @@
           <t>ÅVS mat- och restavfall</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>400.0</t>
@@ -5181,7 +5004,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
           <t>-</t>
@@ -5239,8 +5061,6 @@
           <t>Nyckelbricka till ÅVS</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>160.0</t>
@@ -5256,7 +5076,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
           <t>-</t>
@@ -5267,7 +5086,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5310,8 +5128,6 @@
           <t>Gips- rent utan träreglar</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>1440.0</t>
@@ -5327,7 +5143,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
           <t>-</t>
@@ -5385,8 +5200,6 @@
           <t>Tjänsttaxa för grovavfall</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -5402,7 +5215,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
           <t>-</t>
@@ -5460,8 +5272,6 @@
           <t>Budning av grovavfall, pris per tillfälle</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>1120.0</t>
@@ -5477,7 +5287,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
           <t>-</t>
@@ -5535,8 +5344,6 @@
           <t>Grundavgift flerbostadshus</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>584.0</t>
@@ -5552,7 +5359,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
           <t>-</t>
@@ -5610,8 +5416,6 @@
           <t>Grundavgift permanentboende</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>1320.0</t>
@@ -5627,7 +5431,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
           <t>-</t>
@@ -5685,8 +5488,6 @@
           <t>Grundavgift säsongsboende</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>960.0</t>
@@ -5702,7 +5503,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
           <t>-</t>
@@ -5760,8 +5560,6 @@
           <t>Grundavgift verksamheter</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>1280.0</t>
@@ -5777,7 +5575,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
           <t>-</t>
@@ -5835,8 +5632,6 @@
           <t>Hämtning av farligt avfall, pris per tillfälle</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>400.0</t>
@@ -5852,7 +5647,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
           <t>-</t>
@@ -5910,8 +5704,6 @@
           <t>Inert avfall. (Tex klinker, porslin, toalettstolar)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>1800.0</t>
@@ -5927,7 +5719,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
           <t>-</t>
@@ -5985,8 +5776,6 @@
           <t>Inert avfall. (Tex klinker, porslin, toalettstolar)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>1200.0</t>
@@ -6002,7 +5791,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
           <t>-</t>
@@ -6060,8 +5848,6 @@
           <t>Kärl140L matavfall var 14e dag</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>480.0</t>
@@ -6077,7 +5863,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
           <t>-</t>
@@ -6135,8 +5920,6 @@
           <t>Viktavgift matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>2.24</t>
@@ -6152,7 +5935,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
           <t>-</t>
@@ -6210,8 +5992,6 @@
           <t>Dragväg 1,5-10 meter</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -6227,7 +6007,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
         <is>
           <t>-</t>
@@ -6285,8 +6064,6 @@
           <t>Dragväg 10-20 meter</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -6302,7 +6079,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
           <t>-</t>
@@ -6360,8 +6136,6 @@
           <t>Överviktsavgift över60kg</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>4.24</t>
@@ -6377,7 +6151,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
           <t>-</t>
@@ -6435,8 +6208,6 @@
           <t>Kärl140L matavfall varje vecka</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>960.0</t>
@@ -6452,7 +6223,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
         <is>
           <t>-</t>
@@ -6510,8 +6280,6 @@
           <t>Viktavgift matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
           <t>2.24</t>
@@ -6527,7 +6295,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
           <t>-</t>
@@ -6585,8 +6352,6 @@
           <t>Dragväg 1,5-10 meter</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -6602,7 +6367,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
           <t>-</t>
@@ -6660,8 +6424,6 @@
           <t>Dragväg 10-20 meter</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -6677,7 +6439,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
           <t>-</t>
@@ -6735,8 +6496,6 @@
           <t>Överviktsavgift för vikt över 60 kg, matavfall</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>4.24</t>
@@ -6752,7 +6511,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
           <t>-</t>
@@ -6810,8 +6568,6 @@
           <t>Kärl120-190L rest var 14e dag</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>480.0</t>
@@ -6827,7 +6583,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr">
         <is>
           <t>-</t>
@@ -6885,8 +6640,6 @@
           <t>Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>4.24</t>
@@ -6902,7 +6655,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
           <t>-</t>
@@ -6960,8 +6712,6 @@
           <t>Dragväg 1,5-10 meter</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -6977,7 +6727,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
           <t>-</t>
@@ -7035,8 +6784,6 @@
           <t>Dragväg 10-20 meter</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -7052,7 +6799,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr">
         <is>
           <t>-</t>
@@ -7110,8 +6856,6 @@
           <t>Överviktsavgift för vikt över 60 kg, restavfall</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
           <t>8.48</t>
@@ -7127,7 +6871,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
         <is>
           <t>-</t>
@@ -7185,8 +6928,6 @@
           <t>Kärl120-190L rest varje vecka</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
           <t>960.0</t>
@@ -7202,7 +6943,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
           <t>-</t>
@@ -7260,8 +7000,6 @@
           <t>Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
           <t>4.24</t>
@@ -7277,7 +7015,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
         <is>
           <t>-</t>
@@ -7335,8 +7072,6 @@
           <t>Dragväg 1,5-10 meter</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -7352,7 +7087,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
           <t>-</t>
@@ -7410,8 +7144,6 @@
           <t>Dragväg 10-20 meter</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -7427,7 +7159,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
         <is>
           <t>-</t>
@@ -7485,8 +7216,6 @@
           <t>Överviktsavgift för vikt över 60 kg, restavfall</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
           <t>8.48</t>
@@ -7502,7 +7231,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
           <t>-</t>
@@ -7560,8 +7288,6 @@
           <t>Extra120-190L rest var 14e dag</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>480.0</t>
@@ -7577,7 +7303,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
           <t>-</t>
@@ -7635,8 +7360,6 @@
           <t>Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>4.24</t>
@@ -7652,7 +7375,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
         <is>
           <t>-</t>
@@ -7710,8 +7432,6 @@
           <t>Överviktsavgift för vikt över 60 kg, restavfall</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>8.48</t>
@@ -7727,7 +7447,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
           <t>-</t>
@@ -7785,8 +7504,6 @@
           <t>Extra120-190Lrest/matvar14edag</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -7802,7 +7519,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
           <t>-</t>
@@ -7860,8 +7576,6 @@
           <t>Viktavgift rest- matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -7877,7 +7591,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
           <t>-</t>
@@ -7935,8 +7648,6 @@
           <t>Extra120-190Lrest/matvar14edag</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -7952,7 +7663,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
           <t>-</t>
@@ -8010,8 +7720,6 @@
           <t>Viktavgift rest- matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -8027,7 +7735,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
           <t>-</t>
@@ -8085,8 +7792,6 @@
           <t>Tvåfackskärl 240L, restavfall/kompost. Var 14:e dag säsong</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>480.0</t>
@@ -8102,7 +7807,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
         <is>
           <t>-</t>
@@ -8160,8 +7864,6 @@
           <t>Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
           <t>4.24</t>
@@ -8177,7 +7879,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
         <is>
           <t>-</t>
@@ -8235,8 +7936,6 @@
           <t>Kärl240L, restavfall/kompost. Var 14:e dag</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
           <t>480.0</t>
@@ -8252,7 +7951,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr">
         <is>
           <t>-</t>
@@ -8310,8 +8008,6 @@
           <t>Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>4.24</t>
@@ -8327,7 +8023,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr">
         <is>
           <t>-</t>
@@ -8385,8 +8080,6 @@
           <t>Kärl240L rest/matavfall säsong</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
           <t>480.0</t>
@@ -8402,7 +8095,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
           <t>-</t>
@@ -8460,8 +8152,6 @@
           <t>Viktavgift rest- matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -8477,7 +8167,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
           <t>-</t>
@@ -8535,8 +8224,6 @@
           <t>Kärl 240L rest/mat var 14e dag</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
           <t>480.0</t>
@@ -8552,7 +8239,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
           <t>-</t>
@@ -8610,8 +8296,6 @@
           <t>Viktavgift rest- matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -8627,7 +8311,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
         <is>
           <t>-</t>
@@ -8685,8 +8368,6 @@
           <t>Kärl 240L rest/mat var 14e dag</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
           <t>480.0</t>
@@ -8702,7 +8383,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr">
         <is>
           <t>-</t>
@@ -8760,8 +8440,6 @@
           <t>Viktavgift rest- matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -8777,7 +8455,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr">
         <is>
           <t>-</t>
@@ -8835,8 +8512,6 @@
           <t>Dragväg 1,5-10 meter</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -8852,7 +8527,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
           <t>-</t>
@@ -8910,8 +8584,6 @@
           <t>Dragväg 10-20 meter</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -8927,7 +8599,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
           <t>-</t>
@@ -8985,8 +8656,6 @@
           <t>Kärl 240L rest/mat varje vecka</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
           <t>960.0</t>
@@ -9002,7 +8671,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
           <t>-</t>
@@ -9060,8 +8728,6 @@
           <t>Viktavgift rest- matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -9077,7 +8743,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
           <t>-</t>
@@ -9135,8 +8800,6 @@
           <t>Dragväg 1,5-10 meter</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -9152,7 +8815,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr">
         <is>
           <t>-</t>
@@ -9210,8 +8872,6 @@
           <t>Dragväg 10-20 meter</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -9227,7 +8887,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr">
         <is>
           <t>-</t>
@@ -9285,8 +8944,6 @@
           <t>Kärl370L restavfall var 14edag</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
           <t>800.0</t>
@@ -9302,7 +8959,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
           <t>-</t>
@@ -9360,8 +9016,6 @@
           <t>Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
           <t>4.24</t>
@@ -9377,7 +9031,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
         <is>
           <t>-</t>
@@ -9435,8 +9088,6 @@
           <t>Dragväg 1,5-10 meter</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -9452,7 +9103,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
           <t>-</t>
@@ -9510,8 +9160,6 @@
           <t>Dragväg 10-20 meter</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -9527,7 +9175,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
         <is>
           <t>-</t>
@@ -9585,8 +9232,6 @@
           <t>Överviktsavgift över60kg</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
           <t>8.48</t>
@@ -9602,7 +9247,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
         <is>
           <t>-</t>
@@ -9660,8 +9304,6 @@
           <t>Kärl370Lrestavfall varje vecka</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
           <t>1600.0</t>
@@ -9677,7 +9319,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
           <t>-</t>
@@ -9735,8 +9376,6 @@
           <t>Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
           <t>4.24</t>
@@ -9752,7 +9391,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
         <is>
           <t>-</t>
@@ -9810,8 +9448,6 @@
           <t>Dragväg 1,5-10 meter</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -9827,7 +9463,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr">
         <is>
           <t>-</t>
@@ -9885,8 +9520,6 @@
           <t>Dragväg 10-20 meter</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -9902,7 +9535,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr">
         <is>
           <t>-</t>
@@ -9960,8 +9592,6 @@
           <t>Överviktsavgift för vikt över 60 kg, restavfall</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
           <t>8.48</t>
@@ -9977,7 +9607,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr">
         <is>
           <t>-</t>
@@ -10035,8 +9664,6 @@
           <t>Kärl660L restavfall var 14edag</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
           <t>1280.0</t>
@@ -10052,7 +9679,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr">
         <is>
           <t>-</t>
@@ -10110,8 +9736,6 @@
           <t>Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
           <t>4.24</t>
@@ -10127,7 +9751,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr">
         <is>
           <t>-</t>
@@ -10185,8 +9808,6 @@
           <t>Dragväg 1,5-10 meter</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -10202,7 +9823,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr">
         <is>
           <t>-</t>
@@ -10260,8 +9880,6 @@
           <t>Dragväg 10-20 meter</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -10277,7 +9895,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr">
         <is>
           <t>-</t>
@@ -10335,8 +9952,6 @@
           <t>Överviktsavgift för vikt över 100 kg, restavfall</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
           <t>8.48</t>
@@ -10352,7 +9967,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
           <t>-</t>
@@ -10410,8 +10024,6 @@
           <t>Kärl660Lrestavfall varje vecka</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
           <t>2560.0</t>
@@ -10427,7 +10039,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr">
         <is>
           <t>-</t>
@@ -10485,8 +10096,6 @@
           <t>Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
           <t>4.24</t>
@@ -10502,7 +10111,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
           <t>-</t>
@@ -10560,8 +10168,6 @@
           <t>Dragväg 1,5-10 meter</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -10577,7 +10183,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr">
         <is>
           <t>-</t>
@@ -10635,8 +10240,6 @@
           <t>Dragväg 10-20 meter</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -10652,7 +10255,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr">
         <is>
           <t>-</t>
@@ -10710,8 +10312,6 @@
           <t>Byte/återtag av behållare en (1) ggr/år 140–370 liter</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>240.0</t>
@@ -10727,7 +10327,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr">
         <is>
           <t>-</t>
@@ -10785,8 +10384,6 @@
           <t>Byte/återtag av behållare en (1) ggr/år 660 liter</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
           <t>400.0</t>
@@ -10802,7 +10399,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr">
         <is>
           <t>-</t>
@@ -10860,8 +10456,6 @@
           <t>Inlämning av latrinbehållare på ÅVC</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>320.0</t>
@@ -10877,7 +10471,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr">
         <is>
           <t>-</t>
@@ -10935,8 +10528,6 @@
           <t>Viktavgift matavfall</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>2.24</t>
@@ -10952,7 +10543,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr">
         <is>
           <t>-</t>
@@ -11010,8 +10600,6 @@
           <t>Tjänstetaxa underjordsbehållare för matavfall</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11027,7 +10615,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr">
         <is>
           <t>-</t>
@@ -11085,8 +10672,6 @@
           <t>Viktavgift matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
           <t>2.24</t>
@@ -11102,7 +10687,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr">
         <is>
           <t>-</t>
@@ -11160,8 +10744,6 @@
           <t>Tömningsavgift Underjordsbehållare Matavfall</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
           <t>304.0</t>
@@ -11177,7 +10759,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr">
         <is>
           <t>-</t>
@@ -11235,8 +10816,6 @@
           <t>Tömning Markbehållare 1,6 m³, Matavfall</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
           <t>304.0</t>
@@ -11252,7 +10831,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr">
         <is>
           <t>-</t>
@@ -11310,8 +10888,6 @@
           <t>Tjänstetaxa underjordsbehållare för restavfall</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11327,7 +10903,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
         <is>
           <t>-</t>
@@ -11385,8 +10960,6 @@
           <t>Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
           <t>4.24</t>
@@ -11402,7 +10975,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr">
         <is>
           <t>-</t>
@@ -11460,8 +11032,6 @@
           <t>Tömningsavgift Underjordsbehållare Restavfall</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
           <t>304.0</t>
@@ -11477,7 +11047,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr">
         <is>
           <t>-</t>
@@ -11535,8 +11104,6 @@
           <t>Tömning Markbehållare 3,2 m³, Restavfall</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
           <t>304.0</t>
@@ -11552,7 +11119,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr">
         <is>
           <t>-</t>
@@ -11610,8 +11176,6 @@
           <t>Metallskrot- rent</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11627,7 +11191,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr">
         <is>
           <t>-</t>
@@ -11685,8 +11248,6 @@
           <t>Metallskrot- rent</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11702,7 +11263,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr">
         <is>
           <t>-</t>
@@ -11760,8 +11320,6 @@
           <t>Tömning slam, minireningsverk 0-3 m³</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
           <t>1252.0</t>
@@ -11777,7 +11335,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr">
         <is>
           <t>-</t>
@@ -11835,8 +11392,6 @@
           <t>Minireningsverk 0-3 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11852,7 +11407,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr">
         <is>
           <t>-</t>
@@ -11910,8 +11464,6 @@
           <t>Minireningsverk 0-3 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11927,7 +11479,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr">
         <is>
           <t>-</t>
@@ -11985,8 +11536,6 @@
           <t>Tömning slam, minireningsverk 3,1-6 m³</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
           <t>1756.0</t>
@@ -12002,7 +11551,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr">
         <is>
           <t>-</t>
@@ -12060,8 +11608,6 @@
           <t>Minireningsverk 3,1-6 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12077,7 +11623,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr">
         <is>
           <t>-</t>
@@ -12135,8 +11680,6 @@
           <t>Minireningsverk 3,1-6 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12152,7 +11695,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr">
         <is>
           <t>-</t>
@@ -12210,8 +11752,6 @@
           <t>Minireningsverk 6,1-9 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12227,7 +11767,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr">
         <is>
           <t>-</t>
@@ -12285,8 +11824,6 @@
           <t>Minireningsverk 6,1-9 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12302,7 +11839,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr">
         <is>
           <t>-</t>
@@ -12360,8 +11896,6 @@
           <t>Tömning slam, minireningsverk över 6,1 m³</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
           <t>3254.4</t>
@@ -12377,7 +11911,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr">
         <is>
           <t>-</t>
@@ -12435,8 +11968,6 @@
           <t>Minireningsverk över 9 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12452,7 +11983,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr">
         <is>
           <t>-</t>
@@ -12510,8 +12040,6 @@
           <t>Minireningsverk över 9 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12527,7 +12055,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr">
         <is>
           <t>-</t>
@@ -12565,7 +12092,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>1</t>
@@ -12581,8 +12107,6 @@
           <t>Nedtagning VA-mätare</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
           <t>1280.0</t>
@@ -12598,7 +12122,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr">
         <is>
           <t>-</t>
@@ -12656,8 +12179,6 @@
           <t>Tjänsttaxa för ny tjänst matavfall</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12673,7 +12194,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr">
         <is>
           <t>-</t>
@@ -12731,8 +12251,6 @@
           <t>Tjänsttaxa för ny tjänst osorterat avfall</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12748,7 +12266,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr">
         <is>
           <t>-</t>
@@ -12806,8 +12323,6 @@
           <t>Tjänsttaxa för ny tjänst restavfall</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12823,7 +12338,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr">
         <is>
           <t>-</t>
@@ -12881,8 +12395,6 @@
           <t>Tjänsttaxa för ny tjänst matavfall</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12898,7 +12410,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr">
         <is>
           <t>-</t>
@@ -12956,8 +12467,6 @@
           <t>Orderrad för sorterat avfall, ska bytas ut för varje order</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12973,7 +12482,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr">
         <is>
           <t>-</t>
@@ -13031,8 +12539,6 @@
           <t>Orderrad för extratömning</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -13048,7 +12554,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr">
         <is>
           <t>-</t>
@@ -13106,8 +12611,6 @@
           <t>Orderrad för trasigt hjul</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -13123,7 +12626,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr">
         <is>
           <t>-</t>
@@ -13181,8 +12683,6 @@
           <t>Orderrad för trasigt kärl</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -13198,7 +12698,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr">
         <is>
           <t>-</t>
@@ -13256,8 +12755,6 @@
           <t>Orderrad för trasigt lock</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -13273,7 +12770,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr">
         <is>
           <t>-</t>
@@ -13331,8 +12827,6 @@
           <t>Orderrad för trasigt tagg</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -13348,7 +12842,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr">
         <is>
           <t>-</t>
@@ -13386,7 +12879,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
           <t>1</t>
@@ -13402,8 +12894,6 @@
           <t>Påsläpp av vattentillförsel</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
           <t>1280.0</t>
@@ -13419,7 +12909,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr">
         <is>
           <t>-</t>
@@ -13477,8 +12966,6 @@
           <t>Viktavgift restavfall</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
           <t>4.24</t>
@@ -13494,7 +12981,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr">
         <is>
           <t>-</t>
@@ -13552,8 +13038,6 @@
           <t>Fast avgift spillvatten</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
           <t>1135.4</t>
@@ -13569,7 +13053,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr">
         <is>
           <t>-</t>
@@ -13580,7 +13063,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -13623,8 +13105,6 @@
           <t>Förbrukning spillvatten</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
           <t>13.0</t>
@@ -13640,7 +13120,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr">
         <is>
           <t>-</t>
@@ -13651,7 +13130,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -13694,8 +13172,6 @@
           <t>Fast avgift spillvatten</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
           <t>1135.4</t>
@@ -13711,7 +13187,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr">
         <is>
           <t>-</t>
@@ -13722,7 +13197,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -13765,8 +13239,6 @@
           <t>Förbrukning spillvatten</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
           <t>13.0</t>
@@ -13782,7 +13254,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr">
         <is>
           <t>-</t>
@@ -13793,7 +13264,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -13836,8 +13306,6 @@
           <t>Avgift, per lägenhet</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
           <t>1169.0</t>
@@ -13853,7 +13321,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr">
         <is>
           <t>-</t>
@@ -13911,8 +13378,6 @@
           <t>Avgift per påbörjad 150-tal m² bruttoarea</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
           <t>1169.0</t>
@@ -13928,7 +13393,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr">
         <is>
           <t>-</t>
@@ -13986,8 +13450,6 @@
           <t>Framkörningsavgift slamtömning akut inom 48 tim</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
           <t>2616.8</t>
@@ -14003,7 +13465,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr">
         <is>
           <t>-</t>
@@ -14061,8 +13522,6 @@
           <t>Budtillägg</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
           <t>2096.8</t>
@@ -14078,7 +13537,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr">
         <is>
           <t>-</t>
@@ -14136,8 +13594,6 @@
           <t>Budtillägg</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
           <t>2096.8</t>
@@ -14153,7 +13609,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr">
         <is>
           <t>-</t>
@@ -14211,8 +13666,6 @@
           <t>Budtillägg</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
           <t>2096.8</t>
@@ -14228,7 +13681,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr">
         <is>
           <t>-</t>
@@ -14286,8 +13738,6 @@
           <t>Budad hämtning fett från avskiljare</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
           <t>3680.0</t>
@@ -14303,7 +13753,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr">
         <is>
           <t>-</t>
@@ -14361,8 +13810,6 @@
           <t>Framkörningsavgift vid ej genomförd tömning</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
           <t>939.2</t>
@@ -14378,7 +13825,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr">
         <is>
           <t>-</t>
@@ -14436,8 +13882,6 @@
           <t>Tillägg över 3 m³</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
           <t>480.0</t>
@@ -14453,7 +13897,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr">
         <is>
           <t>-</t>
@@ -14511,8 +13954,6 @@
           <t>Tillägg för kubikmeter överstigande 9,1 m³</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
           <t>480.0</t>
@@ -14528,7 +13969,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr">
         <is>
           <t>-</t>
@@ -14586,8 +14026,6 @@
           <t>Budad hämtning av olja från avskiljare</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
           <t>3680.0</t>
@@ -14603,7 +14041,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr">
         <is>
           <t>-</t>
@@ -14661,8 +14098,6 @@
           <t>Total slangdragning, 10 m</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -14678,7 +14113,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr">
         <is>
           <t>-</t>
@@ -14736,8 +14170,6 @@
           <t>Total slangdragning, 20 m</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
           <t>240.0</t>
@@ -14753,7 +14185,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr">
         <is>
           <t>-</t>
@@ -14811,8 +14242,6 @@
           <t>Total slangdragning, 30 m</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
           <t>320.0</t>
@@ -14828,7 +14257,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr">
         <is>
           <t>-</t>
@@ -14886,8 +14314,6 @@
           <t>Tillägg för var 10 meter slang över 40 meter</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
           <t>415.2</t>
@@ -14903,7 +14329,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr">
         <is>
           <t>-</t>
@@ -14961,8 +14386,6 @@
           <t>Total slangdragning, 40 m</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
           <t>375.2</t>
@@ -14978,7 +14401,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr">
         <is>
           <t>-</t>
@@ -15036,8 +14458,6 @@
           <t>Tillägg för specificerad inställelsetid för tömning</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
           <t>1080.0</t>
@@ -15053,7 +14473,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr">
         <is>
           <t>-</t>
@@ -15111,8 +14530,6 @@
           <t>Statistik vikt slam</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -15128,7 +14545,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr">
         <is>
           <t>-</t>
@@ -15186,8 +14602,6 @@
           <t>Tömning slam, sluten tank 0-3 m³</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
           <t>1252.0</t>
@@ -15203,7 +14617,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr">
         <is>
           <t>-</t>
@@ -15261,8 +14674,6 @@
           <t>Sluten tank 0-3 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -15278,7 +14689,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr">
         <is>
           <t>-</t>
@@ -15336,8 +14746,6 @@
           <t>Sluten tank 0-3 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -15353,7 +14761,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr">
         <is>
           <t>-</t>
@@ -15411,8 +14818,6 @@
           <t>Tömning slam, sluten tank 3,1-6 m³</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
           <t>1756.0</t>
@@ -15428,7 +14833,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr">
         <is>
           <t>-</t>
@@ -15486,8 +14890,6 @@
           <t>Sluten tank 3,1-6 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -15503,7 +14905,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr">
         <is>
           <t>-</t>
@@ -15561,8 +14962,6 @@
           <t>Sluten tank 3,1-6 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -15578,7 +14977,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr">
         <is>
           <t>-</t>
@@ -15636,8 +15034,6 @@
           <t>Tömning slam, sluten tank 6,1-9 m³</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
           <t>3254.4</t>
@@ -15653,7 +15049,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr">
         <is>
           <t>-</t>
@@ -15711,8 +15106,6 @@
           <t>Sluten tank 6,1-9 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -15728,7 +15121,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr">
         <is>
           <t>-</t>
@@ -15786,8 +15178,6 @@
           <t>Sluten tank 6,1-9 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -15803,7 +15193,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr">
         <is>
           <t>-</t>
@@ -15861,8 +15250,6 @@
           <t>Tillägg lyft av tungt brunnslock över 15 kg</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
           <t>556.0</t>
@@ -15878,7 +15265,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N200" t="inlineStr"/>
       <c r="O200" t="inlineStr">
         <is>
           <t>-</t>
@@ -15936,8 +15322,6 @@
           <t>Sluten tank över 9 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -15953,7 +15337,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr">
         <is>
           <t>-</t>
@@ -16011,8 +15394,6 @@
           <t>Sluten tank över 9 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -16028,7 +15409,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr">
         <is>
           <t>-</t>
@@ -16086,8 +15466,6 @@
           <t>Sorterat avfall, ska bytas ut för varje order</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -16103,7 +15481,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr">
         <is>
           <t>-</t>
@@ -16161,8 +15538,6 @@
           <t>Sorterat avfall, ska bytas ut för varje order</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -16178,7 +15553,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr">
         <is>
           <t>-</t>
@@ -16236,8 +15610,6 @@
           <t>Material till sortering</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
           <t>4000.0</t>
@@ -16253,7 +15625,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr">
         <is>
           <t>-</t>
@@ -16311,8 +15682,6 @@
           <t>Material till sortering</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
           <t>6000.0</t>
@@ -16328,7 +15697,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr">
         <is>
           <t>-</t>
@@ -16366,7 +15734,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
           <t>1</t>
@@ -16382,8 +15749,6 @@
           <t>Montering och demontering av strypbricka i vattenmätare</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
           <t>1280.0</t>
@@ -16399,7 +15764,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr">
         <is>
           <t>-</t>
@@ -16457,8 +15821,6 @@
           <t>Fast avgift spillvatten</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
           <t>1135.4</t>
@@ -16474,7 +15836,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr">
         <is>
           <t>-</t>
@@ -16485,7 +15846,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -16528,8 +15888,6 @@
           <t>Uppsk förbrukning spillvatten</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
           <t>13.0</t>
@@ -16545,7 +15903,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr">
         <is>
           <t>-</t>
@@ -16556,7 +15913,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -16599,8 +15955,6 @@
           <t>Fast avgift spillvatten</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
           <t>1135.4</t>
@@ -16616,7 +15970,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr">
         <is>
           <t>-</t>
@@ -16627,7 +15980,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -16670,8 +16022,6 @@
           <t>Uppsk förbrukning spillvatten</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
           <t>13.0</t>
@@ -16687,7 +16037,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr">
         <is>
           <t>-</t>
@@ -16698,7 +16047,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -16741,8 +16089,6 @@
           <t>Avgift, per lägenhet</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
           <t>1169.0</t>
@@ -16758,7 +16104,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr">
         <is>
           <t>-</t>
@@ -16816,8 +16161,6 @@
           <t>Avgift per påbörjad 150-tal m² bruttoarea</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
           <t>1169.0</t>
@@ -16833,7 +16176,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr">
         <is>
           <t>-</t>
@@ -16891,16 +16233,11 @@
           <t>240L kärl/4e vecka 2 facks metall o textil test</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
       <c r="M214" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr">
         <is>
           <t>-</t>
@@ -16958,16 +16295,11 @@
           <t>240L kärl/4e vecka 2 facks metall o textil test</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr">
         <is>
           <t>-</t>
@@ -17025,16 +16357,11 @@
           <t>240L kärl/4e vecka 2 facks färgat o ofärgat glas test</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr">
         <is>
           <t>X</t>
@@ -17092,16 +16419,11 @@
           <t>240L kärl/4e vecka 2 facks färgat o ofärgat glas test</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
       <c r="M217" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr">
         <is>
           <t>X</t>
@@ -17159,16 +16481,11 @@
           <t>370 I Kärl/14 dgr TEST papper plast</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
       <c r="M218" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr">
         <is>
           <t>X</t>
@@ -17226,16 +16543,11 @@
           <t>370 I Kärl - viktavgift papper och plast TEST</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
       <c r="M219" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr">
         <is>
           <t>X</t>
@@ -17293,8 +16605,6 @@
           <t>Träavfall- behandlat</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
           <t>1680.0</t>
@@ -17310,7 +16620,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr">
         <is>
           <t>-</t>
@@ -17368,8 +16677,6 @@
           <t>Träavfall- behandlat</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
           <t>1800.0</t>
@@ -17385,7 +16692,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr">
         <is>
           <t>-</t>
@@ -17443,8 +16749,6 @@
           <t>Trädgårdsavfall</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
           <t>280.0</t>
@@ -17460,7 +16764,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr">
         <is>
           <t>-</t>
@@ -17518,8 +16821,6 @@
           <t>Träavfall- rent</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr"/>
-      <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
           <t>944.0</t>
@@ -17535,7 +16836,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr">
         <is>
           <t>-</t>
@@ -17593,8 +16893,6 @@
           <t>Träavfall- rent</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
           <t>1100.0</t>
@@ -17610,7 +16908,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr">
         <is>
           <t>-</t>
@@ -17668,8 +16965,6 @@
           <t>Tömningar container, matavfall</t>
         </is>
       </c>
-      <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -17685,7 +16980,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr">
         <is>
           <t>-</t>
@@ -17743,8 +17037,6 @@
           <t>Tömningar container, restavfall</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -17760,7 +17052,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr">
         <is>
           <t>-</t>
@@ -17818,8 +17109,6 @@
           <t>Tömningar underjordsbehållare, matavfall</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -17835,7 +17124,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr">
         <is>
           <t>-</t>
@@ -17893,8 +17181,6 @@
           <t>Tömningar underjordsbehållare, restavfall</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -17910,7 +17196,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr">
         <is>
           <t>-</t>
@@ -17968,8 +17253,6 @@
           <t>Tjänsttaxa underjordsbehållare för matavfall</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -17985,7 +17268,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr">
         <is>
           <t>-</t>
@@ -18043,8 +17325,6 @@
           <t>Tjänsttaxa underjordsbehållare för restavfall</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr"/>
-      <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -18060,7 +17340,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr">
         <is>
           <t>-</t>
@@ -18098,7 +17377,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
           <t>1</t>
@@ -18114,8 +17392,6 @@
           <t>Undersökning av vattenmätare</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
           <t>1120.0</t>
@@ -18131,7 +17407,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr">
         <is>
           <t>-</t>
@@ -18169,7 +17444,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
           <t>1</t>
@@ -18185,8 +17459,6 @@
           <t>Uppsättning VA-mätare</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
           <t>1120.0</t>
@@ -18202,7 +17474,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr">
         <is>
           <t>-</t>
@@ -18260,8 +17531,6 @@
           <t>Fast avgift vatten</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr"/>
-      <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
           <t>1226.4</t>
@@ -18277,7 +17546,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr">
         <is>
           <t>-</t>
@@ -18288,7 +17556,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -18331,8 +17598,6 @@
           <t>Avgift per m³ levererat vatten</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
           <t>15.0</t>
@@ -18348,7 +17613,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr">
         <is>
           <t>-</t>
@@ -18359,7 +17623,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -18402,8 +17665,6 @@
           <t>Avgift, per lägenhet</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
           <t>1262.1</t>
@@ -18419,7 +17680,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr">
         <is>
           <t>-</t>
@@ -18477,8 +17737,6 @@
           <t>Avgift per påbörjad 150-tal m² bruttoarea</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
           <t>1262.1</t>
@@ -18494,7 +17752,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr">
         <is>
           <t>-</t>
@@ -18552,8 +17809,6 @@
           <t>Fast avgift vatten</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
           <t>1226.4</t>
@@ -18569,7 +17824,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr">
         <is>
           <t>-</t>
@@ -18580,7 +17834,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -18623,8 +17876,6 @@
           <t>Avgift per m³ levererat vatten</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
           <t>15.0</t>
@@ -18640,7 +17891,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N238" t="inlineStr"/>
       <c r="O238" t="inlineStr">
         <is>
           <t>-</t>
@@ -18651,7 +17901,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -18694,8 +17943,6 @@
           <t>Avgift, per lägenhet</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
           <t>1262.0</t>
@@ -18711,7 +17958,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr">
         <is>
           <t>-</t>
@@ -18769,8 +18015,6 @@
           <t>Avgift per påbörjad 150-tal m² bruttoarea</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
           <t>1262.0</t>
@@ -18786,7 +18030,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr">
         <is>
           <t>-</t>
@@ -18844,8 +18087,6 @@
           <t>Avgift per m³ levererat vatten</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr"/>
-      <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
           <t>13.0</t>
@@ -18861,7 +18102,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N241" t="inlineStr"/>
       <c r="O241" t="inlineStr">
         <is>
           <t>-</t>
@@ -18872,7 +18112,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -18915,8 +18154,6 @@
           <t>Viktavgift matavfall</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr"/>
-      <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
           <t>2.24</t>
@@ -18932,7 +18169,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N242" t="inlineStr"/>
       <c r="O242" t="inlineStr">
         <is>
           <t>-</t>
@@ -18990,8 +18226,6 @@
           <t>Överviktsavgift för vikt över 60 kg, matavfall</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr"/>
-      <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
           <t>8.48</t>
@@ -19007,7 +18241,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N243" t="inlineStr"/>
       <c r="O243" t="inlineStr">
         <is>
           <t>-</t>
@@ -19065,8 +18298,6 @@
           <t>viktavgift matavfall</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
           <t>2.24</t>
@@ -19082,7 +18313,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N244" t="inlineStr"/>
       <c r="O244" t="inlineStr">
         <is>
           <t>-</t>
@@ -19140,8 +18370,6 @@
           <t>Viktavgift restavfall</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
           <t>4.24</t>
@@ -19157,7 +18385,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N245" t="inlineStr"/>
       <c r="O245" t="inlineStr">
         <is>
           <t>-</t>
@@ -19215,8 +18442,6 @@
           <t>Överviktsavgift för vikt över 60 kg, restavfall</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
           <t>8.48</t>
@@ -19232,7 +18457,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N246" t="inlineStr"/>
       <c r="O246" t="inlineStr">
         <is>
           <t>-</t>
@@ -19290,8 +18514,6 @@
           <t>viktavgift restavfall</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr"/>
-      <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
           <t>4.24</t>
@@ -19307,7 +18529,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N247" t="inlineStr"/>
       <c r="O247" t="inlineStr">
         <is>
           <t>-</t>
@@ -19345,7 +18566,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
           <t>1</t>
@@ -19361,16 +18581,11 @@
           <t>Dummytaxa för tjänst</t>
         </is>
       </c>
-      <c r="I248" t="inlineStr"/>
-      <c r="J248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
-      <c r="L248" t="inlineStr"/>
       <c r="M248" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N248" t="inlineStr"/>
       <c r="O248" t="inlineStr">
         <is>
           <t>-</t>
@@ -19381,7 +18596,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -19424,8 +18638,6 @@
           <t>Fast avgift vatten/spillvatten</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr"/>
-      <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
           <t>1752.0</t>
@@ -19441,7 +18653,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N249" t="inlineStr"/>
       <c r="O249" t="inlineStr">
         <is>
           <t>-</t>
@@ -19452,7 +18663,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -19495,8 +18705,6 @@
           <t>Rörlig avgift, förbrukn per m³</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr"/>
-      <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
           <t>30.0</t>
@@ -19512,7 +18720,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N250" t="inlineStr"/>
       <c r="O250" t="inlineStr">
         <is>
           <t>-</t>
@@ -19523,7 +18730,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -19566,8 +18772,6 @@
           <t>Avgift, per lägenhet</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr"/>
-      <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
           <t>1803.0</t>
@@ -19583,7 +18787,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N251" t="inlineStr"/>
       <c r="O251" t="inlineStr">
         <is>
           <t>-</t>
@@ -19641,8 +18844,6 @@
           <t>Avgift per påbörjad 150-tal m² bruttoarea</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr"/>
-      <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
           <t>1803.0</t>
@@ -19658,7 +18859,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N252" t="inlineStr"/>
       <c r="O252" t="inlineStr">
         <is>
           <t>-</t>
@@ -19716,8 +18916,6 @@
           <t>Fast avgift vatten/spillvatten</t>
         </is>
       </c>
-      <c r="I253" t="inlineStr"/>
-      <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
           <t>1752.0</t>
@@ -19733,7 +18931,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N253" t="inlineStr"/>
       <c r="O253" t="inlineStr">
         <is>
           <t>-</t>
@@ -19744,7 +18941,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -19787,8 +18983,6 @@
           <t>Rörlig avgift, förbrukn per m³</t>
         </is>
       </c>
-      <c r="I254" t="inlineStr"/>
-      <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
           <t>30.0</t>
@@ -19804,7 +18998,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N254" t="inlineStr"/>
       <c r="O254" t="inlineStr">
         <is>
           <t>-</t>
@@ -19815,7 +19008,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -19858,8 +19050,6 @@
           <t>Avgift, per lägenhet</t>
         </is>
       </c>
-      <c r="I255" t="inlineStr"/>
-      <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
           <t>1803.0</t>
@@ -19875,7 +19065,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N255" t="inlineStr"/>
       <c r="O255" t="inlineStr">
         <is>
           <t>-</t>
@@ -19933,8 +19122,6 @@
           <t>Avgift per påbörjad 150-tal m² bruttoarea</t>
         </is>
       </c>
-      <c r="I256" t="inlineStr"/>
-      <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
           <t>1803.0</t>
@@ -19950,7 +19137,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N256" t="inlineStr"/>
       <c r="O256" t="inlineStr">
         <is>
           <t>-</t>
@@ -20008,8 +19194,6 @@
           <t>Rörlig avgift, förbrukn per m³</t>
         </is>
       </c>
-      <c r="I257" t="inlineStr"/>
-      <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
           <t>30.0</t>
@@ -20025,7 +19209,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N257" t="inlineStr"/>
       <c r="O257" t="inlineStr">
         <is>
           <t>-</t>
@@ -20036,7 +19219,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -20059,7 +19241,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
           <t>1</t>
@@ -20075,16 +19256,11 @@
           <t>Korrigering av händelse, konto och pris sätts manuellt</t>
         </is>
       </c>
-      <c r="I258" t="inlineStr"/>
-      <c r="J258" t="inlineStr"/>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr"/>
       <c r="M258" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N258" t="inlineStr"/>
       <c r="O258" t="inlineStr">
         <is>
           <t>-</t>
@@ -20095,7 +19271,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -20138,8 +19313,6 @@
           <t>Fast avgift vatten/spillvatten</t>
         </is>
       </c>
-      <c r="I259" t="inlineStr"/>
-      <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr">
         <is>
           <t>1752.0</t>
@@ -20155,7 +19328,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N259" t="inlineStr"/>
       <c r="O259" t="inlineStr">
         <is>
           <t>-</t>
@@ -20166,7 +19338,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -20209,8 +19380,6 @@
           <t>Uppsk förbrukning per m³</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
           <t>30.0</t>
@@ -20226,7 +19395,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N260" t="inlineStr"/>
       <c r="O260" t="inlineStr">
         <is>
           <t>-</t>
@@ -20237,7 +19405,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -20280,8 +19447,6 @@
           <t>Fast avgift vatten/spillvatten</t>
         </is>
       </c>
-      <c r="I261" t="inlineStr"/>
-      <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
           <t>1752.0</t>
@@ -20297,7 +19462,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N261" t="inlineStr"/>
       <c r="O261" t="inlineStr">
         <is>
           <t>-</t>
@@ -20308,7 +19472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -20351,8 +19514,6 @@
           <t>Uppsk förbrukning per m³</t>
         </is>
       </c>
-      <c r="I262" t="inlineStr"/>
-      <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr">
         <is>
           <t>30.0</t>
@@ -20368,7 +19529,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N262" t="inlineStr"/>
       <c r="O262" t="inlineStr">
         <is>
           <t>-</t>
@@ -20379,7 +19539,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -20422,8 +19581,6 @@
           <t>Avgift, per lägenhet</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr"/>
-      <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
           <t>1803.0</t>
@@ -20439,7 +19596,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N263" t="inlineStr"/>
       <c r="O263" t="inlineStr">
         <is>
           <t>-</t>
@@ -20497,8 +19653,6 @@
           <t>Avgift per påbörjad 150-tal m² bruttoarea</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr"/>
-      <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
           <t>1803.0</t>
@@ -20514,7 +19668,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N264" t="inlineStr"/>
       <c r="O264" t="inlineStr">
         <is>
           <t>-</t>
@@ -20572,8 +19725,6 @@
           <t>Fast avgift vatten</t>
         </is>
       </c>
-      <c r="I265" t="inlineStr"/>
-      <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
           <t>1226.4</t>
@@ -20589,7 +19740,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N265" t="inlineStr"/>
       <c r="O265" t="inlineStr">
         <is>
           <t>-</t>
@@ -20600,7 +19750,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -20643,8 +19792,6 @@
           <t>Uppsk förbrukning per m³</t>
         </is>
       </c>
-      <c r="I266" t="inlineStr"/>
-      <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
           <t>15.0</t>
@@ -20660,7 +19807,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N266" t="inlineStr"/>
       <c r="O266" t="inlineStr">
         <is>
           <t>-</t>
@@ -20671,7 +19817,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -20714,8 +19859,6 @@
           <t>Fast avgift vatten</t>
         </is>
       </c>
-      <c r="I267" t="inlineStr"/>
-      <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
           <t>1226.4</t>
@@ -20731,7 +19874,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N267" t="inlineStr"/>
       <c r="O267" t="inlineStr">
         <is>
           <t>-</t>
@@ -20742,7 +19884,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -20785,8 +19926,6 @@
           <t>Uppsk förbrukning per m³</t>
         </is>
       </c>
-      <c r="I268" t="inlineStr"/>
-      <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
           <t>15.0</t>
@@ -20802,7 +19941,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N268" t="inlineStr"/>
       <c r="O268" t="inlineStr">
         <is>
           <t>-</t>
@@ -20813,7 +19951,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -20856,8 +19993,6 @@
           <t>Avgift, per lägenhet</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr"/>
-      <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
           <t>1262.0</t>
@@ -20873,7 +20008,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N269" t="inlineStr"/>
       <c r="O269" t="inlineStr">
         <is>
           <t>-</t>
@@ -20931,8 +20065,6 @@
           <t>Avgift per påbörjad 150-tal m² bruttoarea</t>
         </is>
       </c>
-      <c r="I270" t="inlineStr"/>
-      <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr">
         <is>
           <t>1262.0</t>
@@ -20948,7 +20080,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N270" t="inlineStr"/>
       <c r="O270" t="inlineStr">
         <is>
           <t>-</t>
@@ -21006,16 +20137,11 @@
           <t>ÅVS behandling glasförpackningar, färgade</t>
         </is>
       </c>
-      <c r="I271" t="inlineStr"/>
-      <c r="J271" t="inlineStr"/>
-      <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
       <c r="M271" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N271" t="inlineStr"/>
       <c r="O271" t="inlineStr">
         <is>
           <t>-</t>
@@ -21073,16 +20199,11 @@
           <t>ÅVS behandling glasförpackningar, ofärgade</t>
         </is>
       </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
       <c r="M272" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N272" t="inlineStr"/>
       <c r="O272" t="inlineStr">
         <is>
           <t>-</t>
@@ -21140,8 +20261,6 @@
           <t>ÅVS behandling matavfall</t>
         </is>
       </c>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
           <t>2.3</t>
@@ -21157,7 +20276,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N273" t="inlineStr"/>
       <c r="O273" t="inlineStr">
         <is>
           <t>-</t>
@@ -21215,16 +20333,11 @@
           <t>ÅVS behandling metallförpackningar</t>
         </is>
       </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
       <c r="M274" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N274" t="inlineStr"/>
       <c r="O274" t="inlineStr">
         <is>
           <t>-</t>
@@ -21282,16 +20395,11 @@
           <t>ÅVS behandling pappersförpackningar</t>
         </is>
       </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
       <c r="M275" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N275" t="inlineStr"/>
       <c r="O275" t="inlineStr">
         <is>
           <t>-</t>
@@ -21349,16 +20457,11 @@
           <t>ÅVS behandling plastförpackningar</t>
         </is>
       </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
       <c r="M276" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N276" t="inlineStr"/>
       <c r="O276" t="inlineStr">
         <is>
           <t>-</t>
@@ -21416,8 +20519,6 @@
           <t>ÅVS behandling restavfall</t>
         </is>
       </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr">
         <is>
           <t>4.6</t>
@@ -21433,7 +20534,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N277" t="inlineStr"/>
       <c r="O277" t="inlineStr">
         <is>
           <t>-</t>
@@ -21491,16 +20591,11 @@
           <t>ÅVS behandling tidningar</t>
         </is>
       </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
       <c r="M278" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N278" t="inlineStr"/>
       <c r="O278" t="inlineStr">
         <is>
           <t>-</t>
@@ -21558,8 +20653,6 @@
           <t>ÅVS tömning glasförpackningar, färgade</t>
         </is>
       </c>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -21575,7 +20668,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N279" t="inlineStr"/>
       <c r="O279" t="inlineStr">
         <is>
           <t>-</t>
@@ -21633,8 +20725,6 @@
           <t>ÅVS tömning glasförpackningar, ofärgade</t>
         </is>
       </c>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -21650,7 +20740,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N280" t="inlineStr"/>
       <c r="O280" t="inlineStr">
         <is>
           <t>-</t>
@@ -21708,8 +20797,6 @@
           <t>ÅVS tömning matavfall</t>
         </is>
       </c>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
           <t>380.0</t>
@@ -21725,7 +20812,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N281" t="inlineStr"/>
       <c r="O281" t="inlineStr">
         <is>
           <t>-</t>
@@ -21783,8 +20869,6 @@
           <t>ÅVS tömning metallförpackningar</t>
         </is>
       </c>
-      <c r="I282" t="inlineStr"/>
-      <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -21800,7 +20884,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N282" t="inlineStr"/>
       <c r="O282" t="inlineStr">
         <is>
           <t>-</t>
@@ -21858,8 +20941,6 @@
           <t>ÅVS tömning pappersförpackningar</t>
         </is>
       </c>
-      <c r="I283" t="inlineStr"/>
-      <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -21875,7 +20956,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N283" t="inlineStr"/>
       <c r="O283" t="inlineStr">
         <is>
           <t>-</t>
@@ -21933,8 +21013,6 @@
           <t>ÅVS tömning plastförpackningar</t>
         </is>
       </c>
-      <c r="I284" t="inlineStr"/>
-      <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -21950,7 +21028,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N284" t="inlineStr"/>
       <c r="O284" t="inlineStr">
         <is>
           <t>-</t>
@@ -22008,8 +21085,6 @@
           <t>ÅVS tömning restavfall</t>
         </is>
       </c>
-      <c r="I285" t="inlineStr"/>
-      <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr">
         <is>
           <t>380.0</t>
@@ -22025,7 +21100,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N285" t="inlineStr"/>
       <c r="O285" t="inlineStr">
         <is>
           <t>-</t>
@@ -22083,8 +21157,6 @@
           <t>ÅVS tömning tidningar</t>
         </is>
       </c>
-      <c r="I286" t="inlineStr"/>
-      <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -22100,7 +21172,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N286" t="inlineStr"/>
       <c r="O286" t="inlineStr">
         <is>
           <t>-</t>
@@ -22158,16 +21229,11 @@
           <t>Fyllnadsgrad</t>
         </is>
       </c>
-      <c r="I287" t="inlineStr"/>
-      <c r="J287" t="inlineStr"/>
-      <c r="K287" t="inlineStr"/>
-      <c r="L287" t="inlineStr"/>
       <c r="M287" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N287" t="inlineStr"/>
       <c r="O287" t="inlineStr">
         <is>
           <t>-</t>
@@ -22225,16 +21291,11 @@
           <t>ÅVS glasförpackningar, färgade. Tjänsttaxa</t>
         </is>
       </c>
-      <c r="I288" t="inlineStr"/>
-      <c r="J288" t="inlineStr"/>
-      <c r="K288" t="inlineStr"/>
-      <c r="L288" t="inlineStr"/>
       <c r="M288" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N288" t="inlineStr"/>
       <c r="O288" t="inlineStr">
         <is>
           <t>-</t>
@@ -22292,16 +21353,11 @@
           <t>ÅVS glasförpackningar, ofärgade. Tjänsttaxa</t>
         </is>
       </c>
-      <c r="I289" t="inlineStr"/>
-      <c r="J289" t="inlineStr"/>
-      <c r="K289" t="inlineStr"/>
-      <c r="L289" t="inlineStr"/>
       <c r="M289" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N289" t="inlineStr"/>
       <c r="O289" t="inlineStr">
         <is>
           <t>-</t>
@@ -22359,16 +21415,11 @@
           <t>ÅVS matavfall. Tjänsttaxa</t>
         </is>
       </c>
-      <c r="I290" t="inlineStr"/>
-      <c r="J290" t="inlineStr"/>
-      <c r="K290" t="inlineStr"/>
-      <c r="L290" t="inlineStr"/>
       <c r="M290" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N290" t="inlineStr"/>
       <c r="O290" t="inlineStr">
         <is>
           <t>-</t>
@@ -22426,16 +21477,11 @@
           <t>ÅVS metallförpackningar. Tjänsttaxa</t>
         </is>
       </c>
-      <c r="I291" t="inlineStr"/>
-      <c r="J291" t="inlineStr"/>
-      <c r="K291" t="inlineStr"/>
-      <c r="L291" t="inlineStr"/>
       <c r="M291" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N291" t="inlineStr"/>
       <c r="O291" t="inlineStr">
         <is>
           <t>-</t>
@@ -22493,16 +21539,11 @@
           <t>ÅVS pappersförpackningar. Tjänsttaxa</t>
         </is>
       </c>
-      <c r="I292" t="inlineStr"/>
-      <c r="J292" t="inlineStr"/>
-      <c r="K292" t="inlineStr"/>
-      <c r="L292" t="inlineStr"/>
       <c r="M292" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N292" t="inlineStr"/>
       <c r="O292" t="inlineStr">
         <is>
           <t>-</t>
@@ -22560,16 +21601,11 @@
           <t>ÅVS plastförpackningar. Tjänsttaxa</t>
         </is>
       </c>
-      <c r="I293" t="inlineStr"/>
-      <c r="J293" t="inlineStr"/>
-      <c r="K293" t="inlineStr"/>
-      <c r="L293" t="inlineStr"/>
       <c r="M293" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N293" t="inlineStr"/>
       <c r="O293" t="inlineStr">
         <is>
           <t>-</t>
@@ -22627,16 +21663,11 @@
           <t>ÅVS restavfall. Tjänsttaxa</t>
         </is>
       </c>
-      <c r="I294" t="inlineStr"/>
-      <c r="J294" t="inlineStr"/>
-      <c r="K294" t="inlineStr"/>
-      <c r="L294" t="inlineStr"/>
       <c r="M294" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N294" t="inlineStr"/>
       <c r="O294" t="inlineStr">
         <is>
           <t>-</t>
@@ -22694,16 +21725,11 @@
           <t>ÅVS städning. Tjänsttaxa</t>
         </is>
       </c>
-      <c r="I295" t="inlineStr"/>
-      <c r="J295" t="inlineStr"/>
-      <c r="K295" t="inlineStr"/>
-      <c r="L295" t="inlineStr"/>
       <c r="M295" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N295" t="inlineStr"/>
       <c r="O295" t="inlineStr">
         <is>
           <t>-</t>
@@ -22761,16 +21787,11 @@
           <t>ÅVS tidningar. Tjänsttaxa</t>
         </is>
       </c>
-      <c r="I296" t="inlineStr"/>
-      <c r="J296" t="inlineStr"/>
-      <c r="K296" t="inlineStr"/>
-      <c r="L296" t="inlineStr"/>
       <c r="M296" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N296" t="inlineStr"/>
       <c r="O296" t="inlineStr">
         <is>
           <t>-</t>
@@ -22828,16 +21849,11 @@
           <t>ÅVS vinterhållning. Tjänsttaxa</t>
         </is>
       </c>
-      <c r="I297" t="inlineStr"/>
-      <c r="J297" t="inlineStr"/>
-      <c r="K297" t="inlineStr"/>
-      <c r="L297" t="inlineStr"/>
       <c r="M297" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N297" t="inlineStr"/>
       <c r="O297" t="inlineStr">
         <is>
           <t>-</t>
@@ -22895,8 +21911,6 @@
           <t>Orderrad för ändrat antal. Hemtagning</t>
         </is>
       </c>
-      <c r="I298" t="inlineStr"/>
-      <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -22912,7 +21926,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N298" t="inlineStr"/>
       <c r="O298" t="inlineStr">
         <is>
           <t>-</t>
@@ -22970,8 +21983,6 @@
           <t>Orderrad för ändrat antal kärl, utsättning</t>
         </is>
       </c>
-      <c r="I299" t="inlineStr"/>
-      <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -22987,7 +21998,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N299" t="inlineStr"/>
       <c r="O299" t="inlineStr">
         <is>
           <t>-</t>
@@ -23045,8 +22055,6 @@
           <t>Orderrad för tömningsfrekvensbyte</t>
         </is>
       </c>
-      <c r="I300" t="inlineStr"/>
-      <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -23062,7 +22070,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N300" t="inlineStr"/>
       <c r="O300" t="inlineStr">
         <is>
           <t>-</t>
@@ -23120,8 +22127,6 @@
           <t>Orderrad för kärlbyte storlek, utsättning samt hemtagning</t>
         </is>
       </c>
-      <c r="I301" t="inlineStr"/>
-      <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -23137,7 +22142,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N301" t="inlineStr"/>
       <c r="O301" t="inlineStr">
         <is>
           <t>-</t>
@@ -23195,8 +22199,6 @@
           <t>Orderrad för ny tjänst, utsättning</t>
         </is>
       </c>
-      <c r="I302" t="inlineStr"/>
-      <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -23212,7 +22214,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N302" t="inlineStr"/>
       <c r="O302" t="inlineStr">
         <is>
           <t>-</t>
@@ -23379,7 +22380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -23492,35 +22493,6 @@
       <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Kommentar</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Malå</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>EDP Standardtaxor / regelverk / manuell granskning</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Ej granskad</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>EDP-data får aldrig blandas mellan projekt.</t>
         </is>
       </c>
     </row>
@@ -23700,7 +22672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -23807,46 +22779,6 @@
       <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Kommentar</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Malå</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Taxakod</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Ej satt</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Befintlig Taxa_från_edp är fast. Standardtaxor får endast ge förslag/avvikelse.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Regelverk</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>Ej granskad</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Standardflik för framtida spårning.</t>
         </is>
       </c>
     </row>
@@ -30432,7 +29364,6 @@
         </is>
       </c>
     </row>
-    <row r="216"/>
     <row r="217">
       <c r="D217" s="18" t="inlineStr">
         <is>
@@ -30593,7 +29524,6 @@
         </is>
       </c>
     </row>
-    <row r="222"/>
     <row r="223">
       <c r="D223" s="18" t="inlineStr">
         <is>
@@ -30754,7 +29684,6 @@
         </is>
       </c>
     </row>
-    <row r="228"/>
     <row r="229">
       <c r="D229" s="18" t="inlineStr">
         <is>
@@ -30915,7 +29844,6 @@
         </is>
       </c>
     </row>
-    <row r="234"/>
     <row r="235">
       <c r="D235" s="18" t="inlineStr">
         <is>
@@ -31076,7 +30004,6 @@
         </is>
       </c>
     </row>
-    <row r="240"/>
     <row r="241">
       <c r="D241" s="18" t="inlineStr">
         <is>
@@ -31237,7 +30164,6 @@
         </is>
       </c>
     </row>
-    <row r="246"/>
     <row r="247">
       <c r="D247" s="18" t="inlineStr">
         <is>
@@ -31398,7 +30324,6 @@
         </is>
       </c>
     </row>
-    <row r="252"/>
     <row r="253">
       <c r="D253" s="18" t="inlineStr">
         <is>
@@ -31559,7 +30484,6 @@
         </is>
       </c>
     </row>
-    <row r="258"/>
     <row r="259">
       <c r="D259" s="18" t="inlineStr">
         <is>
@@ -31720,7 +30644,6 @@
         </is>
       </c>
     </row>
-    <row r="264"/>
     <row r="265">
       <c r="D265" s="18" t="inlineStr">
         <is>
@@ -31881,7 +30804,6 @@
         </is>
       </c>
     </row>
-    <row r="270"/>
     <row r="271">
       <c r="D271" s="18" t="inlineStr">
         <is>
@@ -40658,7 +39580,6 @@
         </is>
       </c>
     </row>
-    <row r="113"/>
     <row r="114">
       <c r="A114" s="44" t="inlineStr">
         <is>
